--- a/testcases/matpower/case14.xlsx
+++ b/testcases/matpower/case14.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="bus"/>
@@ -715,7 +715,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,6 +725,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -847,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -876,8 +882,8 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -895,16 +901,22 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1224,34 +1236,34 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>204</v>
       </c>
     </row>
@@ -1731,10 +1743,10 @@
     <col min="13" max="13" style="17" width="11.862142857142858" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="18" width="11.862142857142858" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="18" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="17" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="19" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="2"/>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1754,7 +1766,7 @@
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -1802,7 +1814,7 @@
       </c>
       <c r="P2" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -1810,7 +1822,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="13">
-        <v>21.7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="13">
         <v>94.2</v>
@@ -1850,7 +1862,7 @@
       </c>
       <c r="P3" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -1858,7 +1870,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="13">
-        <v>21.7</v>
+        <v>2</v>
       </c>
       <c r="D4" s="13">
         <v>94.2</v>
@@ -1898,7 +1910,7 @@
       </c>
       <c r="P4" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -1906,7 +1918,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="13">
-        <v>21.7</v>
+        <v>3</v>
       </c>
       <c r="D5" s="13">
         <v>94.2</v>
@@ -1946,7 +1958,7 @@
       </c>
       <c r="P5" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -1954,7 +1966,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="13">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="D6" s="13">
         <v>94.2</v>
@@ -1994,7 +2006,7 @@
       </c>
       <c r="P6" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -2002,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="13">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="D7" s="13">
         <v>94.2</v>
@@ -2042,7 +2054,7 @@
       </c>
       <c r="P7" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -2050,7 +2062,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="13">
-        <v>21.7</v>
+        <v>30</v>
       </c>
       <c r="D8" s="13">
         <v>94.2</v>
@@ -2090,7 +2102,7 @@
       </c>
       <c r="P8" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -2138,7 +2150,7 @@
       </c>
       <c r="P9" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -2146,7 +2158,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="13">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="D10" s="13">
         <v>94.2</v>
@@ -2186,7 +2198,7 @@
       </c>
       <c r="P10" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -2194,7 +2206,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="13">
-        <v>21.7</v>
+        <v>70</v>
       </c>
       <c r="D11" s="13">
         <v>94.2</v>
@@ -2234,7 +2246,7 @@
       </c>
       <c r="P11" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="16.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="15">
         <v>10</v>
       </c>
@@ -2333,22 +2345,22 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2661,43 +2673,43 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3432,58 +3444,58 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>87</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3668,55 +3680,55 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3741,19 +3753,19 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3787,15 +3799,15 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3812,15 +3824,15 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3863,73 +3875,73 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="16.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="20" t="s">
         <v>40</v>
       </c>
     </row>
